--- a/artfynd/A 58518-2022 artfynd.xlsx
+++ b/artfynd/A 58518-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 58518-2022 artfynd.xlsx
+++ b/artfynd/A 58518-2022 artfynd.xlsx
@@ -1539,7 +1539,7 @@
         <v>122278080</v>
       </c>
       <c r="B9" t="n">
-        <v>99478</v>
+        <v>99488</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 58518-2022 artfynd.xlsx
+++ b/artfynd/A 58518-2022 artfynd.xlsx
@@ -1539,7 +1539,7 @@
         <v>122278080</v>
       </c>
       <c r="B9" t="n">
-        <v>99488</v>
+        <v>99500</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 58518-2022 artfynd.xlsx
+++ b/artfynd/A 58518-2022 artfynd.xlsx
@@ -1539,7 +1539,7 @@
         <v>122278080</v>
       </c>
       <c r="B9" t="n">
-        <v>99500</v>
+        <v>99505</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 58518-2022 artfynd.xlsx
+++ b/artfynd/A 58518-2022 artfynd.xlsx
@@ -1539,7 +1539,7 @@
         <v>122278080</v>
       </c>
       <c r="B9" t="n">
-        <v>99505</v>
+        <v>99514</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1553,11 +1553,6 @@
       </c>
       <c r="E9" t="n">
         <v>345</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Sötgräs</t>
-        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>

--- a/artfynd/A 58518-2022 artfynd.xlsx
+++ b/artfynd/A 58518-2022 artfynd.xlsx
@@ -1539,7 +1539,7 @@
         <v>122278080</v>
       </c>
       <c r="B9" t="n">
-        <v>99514</v>
+        <v>99527</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1553,6 +1553,11 @@
       </c>
       <c r="E9" t="n">
         <v>345</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Sötgräs</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>

--- a/artfynd/A 58518-2022 artfynd.xlsx
+++ b/artfynd/A 58518-2022 artfynd.xlsx
@@ -1539,7 +1539,7 @@
         <v>122278080</v>
       </c>
       <c r="B9" t="n">
-        <v>99527</v>
+        <v>99540</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 58518-2022 artfynd.xlsx
+++ b/artfynd/A 58518-2022 artfynd.xlsx
@@ -1539,7 +1539,7 @@
         <v>122278080</v>
       </c>
       <c r="B9" t="n">
-        <v>99540</v>
+        <v>99543</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 58518-2022 artfynd.xlsx
+++ b/artfynd/A 58518-2022 artfynd.xlsx
@@ -1539,7 +1539,7 @@
         <v>122278080</v>
       </c>
       <c r="B9" t="n">
-        <v>99543</v>
+        <v>99544</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 58518-2022 artfynd.xlsx
+++ b/artfynd/A 58518-2022 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>96413985</v>
       </c>
       <c r="B3" t="n">
-        <v>56395</v>
+        <v>57478</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -847,10 +847,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>614625.9047794355</v>
+        <v>614626</v>
       </c>
       <c r="R3" t="n">
-        <v>6909905.35265054</v>
+        <v>6909906</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>

--- a/artfynd/A 58518-2022 artfynd.xlsx
+++ b/artfynd/A 58518-2022 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>96413985</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 58518-2022 artfynd.xlsx
+++ b/artfynd/A 58518-2022 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>96413985</v>
       </c>
       <c r="B3" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 58518-2022 artfynd.xlsx
+++ b/artfynd/A 58518-2022 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>96413985</v>
       </c>
       <c r="B3" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 58518-2022 artfynd.xlsx
+++ b/artfynd/A 58518-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1534,117 +1534,6 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>122278080</v>
-      </c>
-      <c r="B9" t="n">
-        <v>99544</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>345</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Sötgräs</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Cinna latifolia</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Trevir.) Griseb.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Tunbyn, Mpd</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>614856</v>
-      </c>
-      <c r="R9" t="n">
-        <v>6910035</v>
-      </c>
-      <c r="S9" t="n">
-        <v>10</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Sundsvall</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Medelpad</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Tuna</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>Y-Sun-0534</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2015-09-30</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2015-09-30</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Sofia Lund</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Stefan Grundström</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 58518-2022 artfynd.xlsx
+++ b/artfynd/A 58518-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>56075958</v>
       </c>
       <c r="B2" t="n">
-        <v>97598</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100437</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -720,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>614856.4123546197</v>
+        <v>614856</v>
       </c>
       <c r="R2" t="n">
-        <v>6910035.199123787</v>
+        <v>6910035</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -753,19 +748,9 @@
           <t>2015-09-30</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2015-09-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,32 +777,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96413985</v>
+        <v>98084833</v>
       </c>
       <c r="B3" t="n">
-        <v>57490</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56925</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100045</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -831,16 +811,9 @@
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Krokforsen stigen, Mpd</t>
@@ -877,22 +850,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-10-02</t>
+          <t>2022-01-12</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-10-02</t>
+          <t>2022-01-12</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,11 +876,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -927,16 +895,11 @@
         <v>96922244</v>
       </c>
       <c r="B4" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -972,10 +935,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>614625.9047794355</v>
+        <v>614626</v>
       </c>
       <c r="R4" t="n">
-        <v>6909905.35265054</v>
+        <v>6909906</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1044,58 +1007,57 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>97069392</v>
+        <v>112748387</v>
       </c>
       <c r="B5" t="n">
-        <v>56812</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102999</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Krokforsen stigen, Mpd</t>
+          <t>Grenforsens NR, Tuna, Mpd 754 m SW, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>614625.9047794355</v>
+        <v>614589</v>
       </c>
       <c r="R5" t="n">
-        <v>6909905.35265054</v>
+        <v>6909911</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1122,22 +1084,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-11-09</t>
+          <t>2023-10-15</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-11-09</t>
+          <t>2023-10-15</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1152,54 +1114,49 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Maria Lagerborg</t>
+          <t>Thomas Olsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Maria Lagerborg</t>
+          <t>Thomas Olsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>101361698</v>
+        <v>116022925</v>
       </c>
       <c r="B6" t="n">
-        <v>55903</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57899</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102961</v>
+        <v>100067</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Drillsnäppa</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Actitis hypoleucos</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1216,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>614625.9047794355</v>
+        <v>614626</v>
       </c>
       <c r="R6" t="n">
-        <v>6909905.35265054</v>
+        <v>6909906</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1246,22 +1203,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-06-01</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-06-01</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1288,15 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112748387</v>
+        <v>96413985</v>
       </c>
       <c r="B7" t="n">
-        <v>56761</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1304,16 +1256,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1327,23 +1279,26 @@
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Grenforsens NR, Tuna, Mpd 754 m SW, Mpd</t>
+          <t>Krokforsen stigen, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>614589</v>
+        <v>614626</v>
       </c>
       <c r="R7" t="n">
-        <v>6909911</v>
+        <v>6909906</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1370,22 +1325,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-10-15</t>
+          <t>2021-10-02</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-10-15</t>
+          <t>2021-10-02</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1396,31 +1351,31 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Thomas Olsson</t>
+          <t>Maria Lagerborg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Thomas Olsson</t>
+          <t>Maria Lagerborg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>116022925</v>
+        <v>101361698</v>
       </c>
       <c r="B8" t="n">
-        <v>57181</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57369</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1428,26 +1383,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100067</v>
+        <v>102961</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Drillsnäppa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Actitis hypoleucos</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1494,22 +1449,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2022-06-01</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2022-06-01</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1533,6 +1488,470 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100529362</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57947</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>102977</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Gröngöling</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picus viridis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Nedfarten Grönsta, Mpd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>614636</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6910091</v>
+      </c>
+      <c r="S9" t="n">
+        <v>50</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2022-05-05</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2022-05-05</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Maria Lagerborg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Maria Lagerborg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>97069392</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58393</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>102999</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Björktrast</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Turdus pilaris</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Krokforsen stigen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>614626</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6909906</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2021-11-09</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2021-11-09</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Maria Lagerborg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Maria Lagerborg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>94912306</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Grenforsens NR, Tuna, Mpd 754 m SW, Mpd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>614589</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6909911</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2021-07-16</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2021-07-16</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Thomas Olsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Thomas Olsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>99641214</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Krokforsen stigen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>614626</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6909906</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2022-04-03</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2022-04-03</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Maria Lagerborg</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Maria Lagerborg</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 58518-2022 artfynd.xlsx
+++ b/artfynd/A 58518-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56075958</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -889,6 +899,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98084833</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1004,6 +1019,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96922244</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1123,6 +1143,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112748387</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1242,6 +1267,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116022925</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1369,6 +1399,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96413985</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1488,6 +1523,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101361698</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1603,6 +1643,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100529362</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1718,6 +1763,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97069392</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1837,6 +1887,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94912306</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1952,8 +2007,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99641214</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>